--- a/design_issues/sonarqube/Summary.xlsx
+++ b/design_issues/sonarqube/Summary.xlsx
@@ -12,14 +12,14 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Issue_patterns" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="169">
   <si>
     <t>Category</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Extract this nested ternary operation into an independent statement.</t>
   </si>
   <si>
-    <t>Cognitive or Computational Complexity</t>
-  </si>
-  <si>
     <t>Framework Best-Practices Violations</t>
   </si>
   <si>
@@ -168,9 +165,6 @@
     <t>Move this array "sort" operation to a separate statement or replace it with "toSorted".</t>
   </si>
   <si>
-    <t>Module Import &amp; Dependency Issues</t>
-  </si>
-  <si>
     <t>'...' is missing in props validation</t>
   </si>
   <si>
@@ -240,9 +234,6 @@
     <t>Set a HttpStatus code reflective of the operation.</t>
   </si>
   <si>
-    <t>'...' is deprecated.</t>
-  </si>
-  <si>
     <t>Add logic to this catch clause or eliminate it and rethrow the exception automatically.</t>
   </si>
   <si>
@@ -276,9 +267,6 @@
     <t>The signature '...' of '...' is deprecated.</t>
   </si>
   <si>
-    <t>Ambiguous spacing after previous element input</t>
-  </si>
-  <si>
     <t>Remove this use of the output from "..."; "..." doesn't return anything.</t>
   </si>
   <si>
@@ -288,9 +276,6 @@
     <t>This condition is covered by the one on line ...</t>
   </si>
   <si>
-    <t>Ambiguous spacing before next element span</t>
-  </si>
-  <si>
     <t>A form label must have accessible text.</t>
   </si>
   <si>
@@ -312,9 +297,6 @@
     <t>Make sure this Django key gets revoked, changed, and removed from the code.</t>
   </si>
   <si>
-    <t>Remove the useless trailing whitespaces at the end of this line.</t>
-  </si>
-  <si>
     <t>This method has ... returns, which is more than the 3 allowed.</t>
   </si>
   <si>
@@ -336,9 +318,6 @@
     <t>Class "..." has ... methods, which is greater than 20 authorized. Split it into smaller classes.</t>
   </si>
   <si>
-    <t>Add a new line at the end of this file.</t>
-  </si>
-  <si>
     <t>Use &lt;address&gt; or &lt;details&gt; or &lt;fieldset&gt; or &lt;optgroup&gt; instead of the group role to ensure accessibility across all devices.</t>
   </si>
   <si>
@@ -541,6 +520,12 @@
   </si>
   <si>
     <t>Control Flow and Conditionals Issues</t>
+  </si>
+  <si>
+    <t>Code Complexity</t>
+  </si>
+  <si>
+    <t>...' is deprecated.</t>
   </si>
 </sst>
 </file>
@@ -914,10 +899,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="81.08984375" customWidth="1"/>
+    <col min="1" max="1" width="88.6328125" customWidth="1"/>
     <col min="2" max="2" width="39.6328125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -933,7 +918,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -977,7 +962,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>27</v>
@@ -1019,7 +1004,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1058,10 +1043,10 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -1145,7 +1130,7 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -1187,7 +1172,7 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <v>11</v>
@@ -1226,10 +1211,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>11</v>
@@ -1268,10 +1253,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -1310,10 +1295,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1352,10 +1337,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1394,10 +1379,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1436,10 +1421,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1478,10 +1463,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>11</v>
@@ -1520,10 +1505,10 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1562,10 +1547,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1604,10 +1589,10 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>9</v>
@@ -1646,10 +1631,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -1688,10 +1673,10 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -1730,10 +1715,10 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -1772,10 +1757,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>12</v>
@@ -1814,10 +1799,10 @@
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="2">
         <v>7</v>
@@ -1856,10 +1841,10 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -1898,10 +1883,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1940,10 +1925,10 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -1982,10 +1967,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2024,10 +2009,10 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2066,10 +2051,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s">
         <v>42</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -2108,10 +2093,10 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2150,10 +2135,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2192,10 +2177,10 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2234,10 +2219,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2276,10 +2261,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2318,10 +2303,10 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2360,10 +2345,10 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2402,10 +2387,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2444,10 +2429,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2486,10 +2471,10 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2528,10 +2513,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2570,7 +2555,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
@@ -2612,10 +2597,10 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2654,10 +2639,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2696,10 +2681,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2738,10 +2723,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2780,7 +2765,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -2822,10 +2807,10 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2864,10 +2849,10 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2906,10 +2891,10 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2948,10 +2933,10 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2990,10 +2975,10 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -3032,10 +3017,10 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -3074,10 +3059,10 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -3116,10 +3101,10 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -3158,7 +3143,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B54" t="s">
         <v>16</v>
@@ -3200,10 +3185,10 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -3242,10 +3227,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -3283,11 +3268,11 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>73</v>
+      <c r="A57" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3326,7 +3311,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
@@ -3368,10 +3353,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -3410,10 +3395,10 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3452,7 +3437,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3494,10 +3479,10 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3536,10 +3521,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3578,10 +3563,10 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3620,10 +3605,10 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3662,10 +3647,10 @@
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -3704,10 +3689,10 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3740,16 +3725,16 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <f t="shared" ref="M67:M128" si="1">SUM(C67:L67)</f>
+        <f t="shared" ref="M67:M124" si="1">SUM(C67:L67)</f>
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3788,10 +3773,10 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3830,10 +3815,10 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3845,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3867,15 +3852,15 @@
       </c>
       <c r="M70">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3887,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3909,39 +3894,39 @@
       </c>
       <c r="M71">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
         <v>2</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -3951,24 +3936,24 @@
       </c>
       <c r="M72">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -3980,10 +3965,10 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -3993,15 +3978,15 @@
       </c>
       <c r="M73">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -4022,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4035,15 +4020,15 @@
       </c>
       <c r="M74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -4055,10 +4040,10 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -4077,15 +4062,15 @@
       </c>
       <c r="M75">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B76" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -4097,16 +4082,16 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4124,10 +4109,10 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -4142,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -4161,15 +4146,15 @@
       </c>
       <c r="M77">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -4184,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -4203,15 +4188,15 @@
       </c>
       <c r="M78">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -4232,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4241,19 +4226,19 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -4292,10 +4277,10 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -4310,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4325,19 +4310,19 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="M81">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -4352,10 +4337,10 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -4367,19 +4352,19 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M82">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -4397,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="H83">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4406,22 +4391,22 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M83">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -4439,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="H84">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4451,19 +4436,19 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M84">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4481,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="H85">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4493,19 +4478,19 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M85">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="B86" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4523,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4535,19 +4520,19 @@
         <v>1</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M86">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>166</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4586,10 +4571,10 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -4607,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -4619,19 +4604,19 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B89" t="s">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4649,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="H89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -4658,22 +4643,22 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M89">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4691,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="H90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4707,15 +4692,15 @@
       </c>
       <c r="M90">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4733,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="H91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4749,15 +4734,15 @@
       </c>
       <c r="M91">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4775,13 +4760,13 @@
         <v>0</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I92">
         <v>0</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -4796,10 +4781,10 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4838,10 +4823,10 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4859,10 +4844,10 @@
         <v>0</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -4871,19 +4856,19 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B95" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -4901,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -4917,15 +4902,15 @@
       </c>
       <c r="M95">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4943,13 +4928,13 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -4959,15 +4944,15 @@
       </c>
       <c r="M96">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4985,13 +4970,13 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K97">
         <v>0</v>
@@ -5001,15 +4986,15 @@
       </c>
       <c r="M97">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -5030,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5039,19 +5024,19 @@
         <v>0</v>
       </c>
       <c r="L98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -5072,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -5085,15 +5070,15 @@
       </c>
       <c r="M99">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -5114,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5127,15 +5112,15 @@
       </c>
       <c r="M100">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -5156,28 +5141,28 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K101">
         <v>0</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>115</v>
+      <c r="A102" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="B102" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -5216,13 +5201,13 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -5253,15 +5238,15 @@
       </c>
       <c r="M103">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -5300,10 +5285,10 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B105" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -5333,19 +5318,19 @@
         <v>0</v>
       </c>
       <c r="L105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M105">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A106" s="4" t="s">
-        <v>171</v>
+      <c r="A106" t="s">
+        <v>115</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -5384,13 +5369,13 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>32</v>
+        <v>165</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -5421,15 +5406,15 @@
       </c>
       <c r="M107">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>13</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -5450,10 +5435,10 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K108">
         <v>0</v>
@@ -5463,15 +5448,15 @@
       </c>
       <c r="M108">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B109" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -5492,10 +5477,10 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K109">
         <v>0</v>
@@ -5505,15 +5490,15 @@
       </c>
       <c r="M109">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B110" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -5534,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K110">
         <v>0</v>
@@ -5547,15 +5532,15 @@
       </c>
       <c r="M110">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -5576,28 +5561,28 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111">
         <v>0</v>
       </c>
       <c r="M111">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -5615,31 +5600,31 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I112">
         <v>0</v>
       </c>
       <c r="J112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M112">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5663,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -5673,15 +5658,15 @@
       </c>
       <c r="M113">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -5705,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114">
         <v>0</v>
@@ -5715,15 +5700,15 @@
       </c>
       <c r="M114">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B115" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5747,25 +5732,25 @@
         <v>0</v>
       </c>
       <c r="J115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="M115">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B116" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5783,31 +5768,31 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I116">
         <v>0</v>
       </c>
       <c r="J116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L116">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M116">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -5831,22 +5816,22 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
@@ -5873,25 +5858,25 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="M118">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B119" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5915,25 +5900,25 @@
         <v>0</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="M119">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -5957,25 +5942,25 @@
         <v>0</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="M120">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B121" t="s">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -6002,22 +5987,22 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="M121">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -6044,22 +6029,22 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B123" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -6086,22 +6071,22 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="M123">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -6128,22 +6113,22 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="M124">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B125" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -6176,16 +6161,16 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M125:M143" si="2">SUM(C125:L125)</f>
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>165</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -6218,16 +6203,16 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -6260,16 +6245,16 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -6296,22 +6281,22 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M128">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -6338,22 +6323,22 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M129">
-        <f t="shared" ref="M129:M147" si="2">SUM(C129:L129)</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B130" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -6380,22 +6365,22 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M130">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B131" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -6422,22 +6407,22 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M131">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B132" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -6467,19 +6452,19 @@
         <v>0</v>
       </c>
       <c r="L132">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M132">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B133" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -6509,19 +6494,19 @@
         <v>0</v>
       </c>
       <c r="L133">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M133">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -6551,19 +6536,19 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M134">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -6593,19 +6578,19 @@
         <v>0</v>
       </c>
       <c r="L135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M135">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B136" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -6635,19 +6620,19 @@
         <v>0</v>
       </c>
       <c r="L136">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M136">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B137" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -6677,19 +6662,19 @@
         <v>0</v>
       </c>
       <c r="L137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M137">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B138" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -6719,19 +6704,19 @@
         <v>0</v>
       </c>
       <c r="L138">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M138">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B139" t="s">
-        <v>173</v>
+        <v>16</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -6761,19 +6746,19 @@
         <v>0</v>
       </c>
       <c r="L139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M139">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B140" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -6803,19 +6788,19 @@
         <v>0</v>
       </c>
       <c r="L140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M140">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B141" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -6854,10 +6839,10 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B142" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -6899,7 +6884,7 @@
         <v>156</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -6908,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -6929,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="L143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143">
         <f t="shared" si="2"/>
@@ -6937,217 +6922,49 @@
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>157</v>
-      </c>
-      <c r="B144" t="s">
-        <v>23</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="E144">
-        <v>0</v>
-      </c>
-      <c r="F144">
-        <v>0</v>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>1</v>
-      </c>
-      <c r="M144">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>158</v>
-      </c>
-      <c r="B145" t="s">
-        <v>172</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145">
-        <v>0</v>
-      </c>
-      <c r="F145">
-        <v>0</v>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>1</v>
-      </c>
-      <c r="M145">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>159</v>
-      </c>
-      <c r="B146" t="s">
-        <v>54</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="E146">
-        <v>0</v>
-      </c>
-      <c r="F146">
-        <v>0</v>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>1</v>
-      </c>
-      <c r="M146">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>163</v>
-      </c>
-      <c r="B147" t="s">
-        <v>172</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147">
-        <v>1</v>
-      </c>
-      <c r="F147">
-        <v>0</v>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C148" s="3">
-        <f t="shared" ref="C148:K148" si="3">SUM(C2:C147)</f>
+      <c r="C144" s="3">
+        <f t="shared" ref="C144:H144" si="3">SUM(C2:C143)</f>
         <v>231</v>
       </c>
-      <c r="D148" s="3">
+      <c r="D144" s="3">
         <f t="shared" si="3"/>
         <v>350</v>
       </c>
-      <c r="E148" s="3">
+      <c r="E144" s="3">
         <f t="shared" si="3"/>
         <v>268</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F144" s="3">
         <f t="shared" si="3"/>
-        <v>259</v>
-      </c>
-      <c r="G148" s="3">
+        <v>253</v>
+      </c>
+      <c r="G144" s="3">
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
-      <c r="H148" s="3">
+      <c r="H144" s="3">
         <f t="shared" si="3"/>
-        <v>148</v>
-      </c>
-      <c r="I148" s="3">
-        <f t="shared" si="3"/>
+        <v>97</v>
+      </c>
+      <c r="I144" s="3">
+        <f t="shared" ref="I144:K144" si="4">SUM(I2:I143)</f>
         <v>584</v>
       </c>
-      <c r="J148" s="3">
-        <f t="shared" si="3"/>
+      <c r="J144" s="3">
+        <f t="shared" si="4"/>
         <v>572</v>
       </c>
-      <c r="K148" s="3">
-        <f t="shared" si="3"/>
+      <c r="K144" s="3">
+        <f t="shared" si="4"/>
         <v>383</v>
       </c>
-      <c r="L148" s="3">
-        <f t="shared" ref="L148" si="4">SUM(L2:L147)</f>
-        <v>419</v>
-      </c>
-      <c r="M148" s="3">
-        <f>SUM(M2:M147)</f>
-        <v>3267</v>
+      <c r="L144" s="3">
+        <f t="shared" ref="L144" si="5">SUM(L2:L143)</f>
+        <v>402</v>
+      </c>
+      <c r="M144" s="3">
+        <f>SUM(M2:M143)</f>
+        <v>3193</v>
       </c>
     </row>
   </sheetData>
